--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/55.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/55.xlsx
@@ -426,13 +426,13 @@
         <v>-3.94350253237807</v>
       </c>
       <c r="E2">
-        <v>-5.650188153025923</v>
+        <v>-8.698693456353499</v>
       </c>
       <c r="F2">
-        <v>-7.28405408058885</v>
+        <v>-8.255776041728129</v>
       </c>
       <c r="G2">
-        <v>0.5409486115396566</v>
+        <v>-2.205324372199374</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.870450721977928</v>
       </c>
       <c r="E3">
-        <v>-6.198346346232396</v>
+        <v>-9.554099554032392</v>
       </c>
       <c r="F3">
-        <v>-7.176144714702072</v>
+        <v>-7.750077362898455</v>
       </c>
       <c r="G3">
-        <v>0.2807066266975486</v>
+        <v>-1.951187033331683</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.88727558576322</v>
       </c>
       <c r="E4">
-        <v>-6.661011478648061</v>
+        <v>-9.833189407125117</v>
       </c>
       <c r="F4">
-        <v>-7.37109139028957</v>
+        <v>-8.088728721399971</v>
       </c>
       <c r="G4">
-        <v>1.292935720239567</v>
+        <v>-2.197451894906988</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.15403536400192</v>
       </c>
       <c r="E5">
-        <v>-6.758423483027058</v>
+        <v>-9.343471170987629</v>
       </c>
       <c r="F5">
-        <v>-7.438192218073782</v>
+        <v>-8.311336008580055</v>
       </c>
       <c r="G5">
-        <v>0.8233944253136565</v>
+        <v>-2.533518614780563</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.6421845186741234</v>
       </c>
       <c r="E6">
-        <v>-7.294807643813589</v>
+        <v>-11.10123458485694</v>
       </c>
       <c r="F6">
-        <v>-7.485119403980647</v>
+        <v>-8.284552374138142</v>
       </c>
       <c r="G6">
-        <v>0.5644369321407857</v>
+        <v>-1.71531066365861</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.3612343674523708</v>
       </c>
       <c r="E7">
-        <v>-8.85181021950085</v>
+        <v>-11.4616422457054</v>
       </c>
       <c r="F7">
-        <v>-7.55765115527538</v>
+        <v>-7.989264467307275</v>
       </c>
       <c r="G7">
-        <v>-0.4088171087673935</v>
+        <v>-3.170606619448989</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.2714051555772146</v>
       </c>
       <c r="E8">
-        <v>-10.22195890068362</v>
+        <v>-11.83953887317148</v>
       </c>
       <c r="F8">
-        <v>-7.520685875503108</v>
+        <v>-8.165985855219896</v>
       </c>
       <c r="G8">
-        <v>0.2692223442218168</v>
+        <v>-3.016788742057832</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3431551911324153</v>
       </c>
       <c r="E9">
-        <v>-10.16230078410657</v>
+        <v>-14.19939460567862</v>
       </c>
       <c r="F9">
-        <v>-7.601399843409958</v>
+        <v>-8.359987850228833</v>
       </c>
       <c r="G9">
-        <v>0.1568789813466491</v>
+        <v>-3.40008370459465</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5228132464086527</v>
       </c>
       <c r="E10">
-        <v>-11.37913344928564</v>
+        <v>-13.64348366497102</v>
       </c>
       <c r="F10">
-        <v>-7.362134741484803</v>
+        <v>-7.820780329787334</v>
       </c>
       <c r="G10">
-        <v>0.02012365566489563</v>
+        <v>-3.219212049056568</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.7612151492503247</v>
       </c>
       <c r="E11">
-        <v>-11.57236796366695</v>
+        <v>-14.6449466348193</v>
       </c>
       <c r="F11">
-        <v>-7.067999772560374</v>
+        <v>-7.954987132399983</v>
       </c>
       <c r="G11">
-        <v>0.3598750127236797</v>
+        <v>-3.665503382660178</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.007152698696601</v>
       </c>
       <c r="E12">
-        <v>-11.45340947995945</v>
+        <v>-15.09553432705651</v>
       </c>
       <c r="F12">
-        <v>-7.082865624062125</v>
+        <v>-7.56082846526823</v>
       </c>
       <c r="G12">
-        <v>-0.2839036044796131</v>
+        <v>-3.310881055038987</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.214005378079601</v>
       </c>
       <c r="E13">
-        <v>-13.23512852132934</v>
+        <v>-15.08524563411108</v>
       </c>
       <c r="F13">
-        <v>-7.101055278353906</v>
+        <v>-7.640940624927214</v>
       </c>
       <c r="G13">
-        <v>-0.8542311478030962</v>
+        <v>-3.719372579675198</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.348729463611833</v>
       </c>
       <c r="E14">
-        <v>-13.01947806061007</v>
+        <v>-16.88494724576543</v>
       </c>
       <c r="F14">
-        <v>-6.845719916578307</v>
+        <v>-7.671633241494908</v>
       </c>
       <c r="G14">
-        <v>0.230293639225527</v>
+        <v>-2.990059397373756</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.390095828592016</v>
       </c>
       <c r="E15">
-        <v>-14.11923608726885</v>
+        <v>-15.88148721887976</v>
       </c>
       <c r="F15">
-        <v>-6.719926155714952</v>
+        <v>-7.086225060235252</v>
       </c>
       <c r="G15">
-        <v>-0.1364121796140032</v>
+        <v>-2.459114103785443</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.334845579832453</v>
       </c>
       <c r="E16">
-        <v>-14.71684974511309</v>
+        <v>-17.4022303031876</v>
       </c>
       <c r="F16">
-        <v>-6.335417008725972</v>
+        <v>-6.929250505455767</v>
       </c>
       <c r="G16">
-        <v>0.3594976105322028</v>
+        <v>-1.762591875050481</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.198717962158233</v>
       </c>
       <c r="E17">
-        <v>-15.26791069015848</v>
+        <v>-17.78040769604216</v>
       </c>
       <c r="F17">
-        <v>-5.978229956190154</v>
+        <v>-7.223876423213981</v>
       </c>
       <c r="G17">
-        <v>0.4180975771228421</v>
+        <v>-1.218470610215869</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.010381640728817</v>
       </c>
       <c r="E18">
-        <v>-15.52050444183233</v>
+        <v>-20.06143175302378</v>
       </c>
       <c r="F18">
-        <v>-5.635582511737506</v>
+        <v>-6.983884796200118</v>
       </c>
       <c r="G18">
-        <v>0.0507130964477614</v>
+        <v>-1.758897306228655</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.8085959576032551</v>
       </c>
       <c r="E19">
-        <v>-17.81300365194938</v>
+        <v>-20.31905211084614</v>
       </c>
       <c r="F19">
-        <v>-5.162233401789556</v>
+        <v>-6.165332932304959</v>
       </c>
       <c r="G19">
-        <v>0.9301363451363773</v>
+        <v>-0.6792357105972212</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.6321578283563051</v>
       </c>
       <c r="E20">
-        <v>-17.97082097111669</v>
+        <v>-20.72811822490701</v>
       </c>
       <c r="F20">
-        <v>-4.904003025600534</v>
+        <v>-5.72064969127942</v>
       </c>
       <c r="G20">
-        <v>0.5578787414274894</v>
+        <v>-0.6554163354421649</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.5134762819035484</v>
       </c>
       <c r="E21">
-        <v>-19.39321012845194</v>
+        <v>-22.28503023111412</v>
       </c>
       <c r="F21">
-        <v>-4.258659493971072</v>
+        <v>-5.677518252525385</v>
       </c>
       <c r="G21">
-        <v>1.065507862782715</v>
+        <v>-0.637287788069116</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.4775459631387526</v>
       </c>
       <c r="E22">
-        <v>-19.65625559813549</v>
+        <v>-23.25284211061141</v>
       </c>
       <c r="F22">
-        <v>-3.996832521648087</v>
+        <v>-5.418096929487953</v>
       </c>
       <c r="G22">
-        <v>0.3300734817791605</v>
+        <v>-1.195468939809013</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.5344353213597983</v>
       </c>
       <c r="E23">
-        <v>-20.58044015904288</v>
+        <v>-22.84948187380019</v>
       </c>
       <c r="F23">
-        <v>-3.899378386288563</v>
+        <v>-4.952003568191588</v>
       </c>
       <c r="G23">
-        <v>0.4285357272081642</v>
+        <v>-1.361165054595075</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6870266094657554</v>
       </c>
       <c r="E24">
-        <v>-21.3014909613882</v>
+        <v>-22.48207772060988</v>
       </c>
       <c r="F24">
-        <v>-3.65069142194598</v>
+        <v>-5.027388761619464</v>
       </c>
       <c r="G24">
-        <v>0.1577099282770062</v>
+        <v>-0.594366565152465</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.9279201987080009</v>
       </c>
       <c r="E25">
-        <v>-21.20906933536565</v>
+        <v>-24.7886106716767</v>
       </c>
       <c r="F25">
-        <v>-3.262714354928666</v>
+        <v>-4.863438774135425</v>
       </c>
       <c r="G25">
-        <v>0.2620682553114518</v>
+        <v>-2.137872006836724</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.240090461915744</v>
       </c>
       <c r="E26">
-        <v>-20.83706878105756</v>
+        <v>-24.56407081648037</v>
       </c>
       <c r="F26">
-        <v>-3.609872193828485</v>
+        <v>-4.898892406611411</v>
       </c>
       <c r="G26">
-        <v>-1.53189319860083</v>
+        <v>-2.08079489119415</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.60144337747519</v>
       </c>
       <c r="E27">
-        <v>-20.96228561584365</v>
+        <v>-24.61456783013991</v>
       </c>
       <c r="F27">
-        <v>-3.406034197305232</v>
+        <v>-4.718070408157239</v>
       </c>
       <c r="G27">
-        <v>-1.045080787596541</v>
+        <v>-2.164786742070999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.980630959322071</v>
       </c>
       <c r="E28">
-        <v>-21.45096683143338</v>
+        <v>-24.41406511497629</v>
       </c>
       <c r="F28">
-        <v>-3.803770060173484</v>
+        <v>-5.030967936988357</v>
       </c>
       <c r="G28">
-        <v>-0.9507169975451548</v>
+        <v>-1.703021918616836</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.347791289618964</v>
       </c>
       <c r="E29">
-        <v>-21.06849191674554</v>
+        <v>-23.46237913142032</v>
       </c>
       <c r="F29">
-        <v>-3.362215430183896</v>
+        <v>-4.919849586990421</v>
       </c>
       <c r="G29">
-        <v>-0.3252490077195709</v>
+        <v>-3.095821395716853</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.673364955828784</v>
       </c>
       <c r="E30">
-        <v>-20.95863566579347</v>
+        <v>-23.53831258358094</v>
       </c>
       <c r="F30">
-        <v>-3.446603199888087</v>
+        <v>-4.511713527375479</v>
       </c>
       <c r="G30">
-        <v>-1.202331700711922</v>
+        <v>-2.080841238831699</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.931476385154232</v>
       </c>
       <c r="E31">
-        <v>-21.0061257727119</v>
+        <v>-25.41186907782638</v>
       </c>
       <c r="F31">
-        <v>-3.767359077471615</v>
+        <v>-4.82812054851521</v>
       </c>
       <c r="G31">
-        <v>-1.103697306914876</v>
+        <v>-2.151104257357191</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.103187380792897</v>
       </c>
       <c r="E32">
-        <v>-20.48133450538501</v>
+        <v>-22.40337737083058</v>
       </c>
       <c r="F32">
-        <v>-3.67451352632602</v>
+        <v>-4.839160562451739</v>
       </c>
       <c r="G32">
-        <v>-1.451771375459388</v>
+        <v>-2.327437154960931</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.174745857440379</v>
       </c>
       <c r="E33">
-        <v>-19.89255590032973</v>
+        <v>-23.22203037346322</v>
       </c>
       <c r="F33">
-        <v>-3.654630098557678</v>
+        <v>-5.299096475148874</v>
       </c>
       <c r="G33">
-        <v>-0.8342718687468301</v>
+        <v>-2.141311663652027</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.140022962809256</v>
       </c>
       <c r="E34">
-        <v>-20.97324452294221</v>
+        <v>-23.76461401516625</v>
       </c>
       <c r="F34">
-        <v>-3.546080519554585</v>
+        <v>-4.785748496747629</v>
       </c>
       <c r="G34">
-        <v>-0.1059121235606977</v>
+        <v>-1.860593954649526</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.999890851005853</v>
       </c>
       <c r="E35">
-        <v>-21.17914970759697</v>
+        <v>-22.45898703164477</v>
       </c>
       <c r="F35">
-        <v>-3.775269688519235</v>
+        <v>-5.164502060513422</v>
       </c>
       <c r="G35">
-        <v>0.2827889598417502</v>
+        <v>-2.274620711427399</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.76233870941631</v>
       </c>
       <c r="E36">
-        <v>-18.74485491935175</v>
+        <v>-23.40138964348502</v>
       </c>
       <c r="F36">
-        <v>-3.843270061263417</v>
+        <v>-4.929046959094336</v>
       </c>
       <c r="G36">
-        <v>-0.221387262516016</v>
+        <v>-1.348568428818148</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.441411889154397</v>
       </c>
       <c r="E37">
-        <v>-19.9737152114952</v>
+        <v>-23.29673208069375</v>
       </c>
       <c r="F37">
-        <v>-4.302821925276058</v>
+        <v>-5.414338003497657</v>
       </c>
       <c r="G37">
-        <v>0.9290074491074859</v>
+        <v>-0.9116823550916083</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.055686219757427</v>
       </c>
       <c r="E38">
-        <v>-19.62168522756093</v>
+        <v>-21.16738020365104</v>
       </c>
       <c r="F38">
-        <v>-4.022248626032017</v>
+        <v>-5.367351032692484</v>
       </c>
       <c r="G38">
-        <v>1.00284916736093</v>
+        <v>-1.820407242348314</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.626426715833985</v>
       </c>
       <c r="E39">
-        <v>-19.16351234136087</v>
+        <v>-22.14054021095138</v>
       </c>
       <c r="F39">
-        <v>-3.974185527057303</v>
+        <v>-4.944110377909039</v>
       </c>
       <c r="G39">
-        <v>0.598317055189687</v>
+        <v>-0.2332754315475388</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.175662891566224</v>
       </c>
       <c r="E40">
-        <v>-18.2269378755685</v>
+        <v>-20.56321837239171</v>
       </c>
       <c r="F40">
-        <v>-4.103061971485062</v>
+        <v>-5.005090182330076</v>
       </c>
       <c r="G40">
-        <v>1.101695436072489</v>
+        <v>0.2354316059024758</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7230415150413345</v>
       </c>
       <c r="E41">
-        <v>-18.49006032931018</v>
+        <v>-21.53978832061983</v>
       </c>
       <c r="F41">
-        <v>-4.029076774086434</v>
+        <v>-5.230265448652045</v>
       </c>
       <c r="G41">
-        <v>1.631842888185837</v>
+        <v>-0.6001136722086398</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.2850819693949866</v>
       </c>
       <c r="E42">
-        <v>-18.26249092500272</v>
+        <v>-20.70311651991067</v>
       </c>
       <c r="F42">
-        <v>-4.230577220678499</v>
+        <v>-5.223349404919322</v>
       </c>
       <c r="G42">
-        <v>1.725451873854269</v>
+        <v>0.6892180146069953</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1278522099559894</v>
       </c>
       <c r="E43">
-        <v>-17.05103355847075</v>
+        <v>-20.59696003222286</v>
       </c>
       <c r="F43">
-        <v>-4.171642772447251</v>
+        <v>-5.338304282497409</v>
       </c>
       <c r="G43">
-        <v>1.893356122515025</v>
+        <v>-0.3459895755231049</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5101351215477584</v>
       </c>
       <c r="E44">
-        <v>-16.90502197104143</v>
+        <v>-20.35341417161634</v>
       </c>
       <c r="F44">
-        <v>-4.279330023579387</v>
+        <v>-5.319073341566228</v>
       </c>
       <c r="G44">
-        <v>1.659009224881097</v>
+        <v>-0.1681669324266924</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.8571623171073995</v>
       </c>
       <c r="E45">
-        <v>-17.18782064434643</v>
+        <v>-19.52418718217579</v>
       </c>
       <c r="F45">
-        <v>-4.273190787598186</v>
+        <v>-5.409386546953035</v>
       </c>
       <c r="G45">
-        <v>2.604544067988958</v>
+        <v>0.5596697465642352</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.165658378207004</v>
       </c>
       <c r="E46">
-        <v>-16.32232510657845</v>
+        <v>-19.13439878196556</v>
       </c>
       <c r="F46">
-        <v>-4.297579066842996</v>
+        <v>-5.420565927010123</v>
       </c>
       <c r="G46">
-        <v>2.112219598661783</v>
+        <v>0.1159407752080216</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.431598195584546</v>
       </c>
       <c r="E47">
-        <v>-15.10471354387006</v>
+        <v>-18.93327113738889</v>
       </c>
       <c r="F47">
-        <v>-4.834049943462616</v>
+        <v>-5.942395442441505</v>
       </c>
       <c r="G47">
-        <v>1.938750322949512</v>
+        <v>0.6650411005336978</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.652006691561913</v>
       </c>
       <c r="E48">
-        <v>-15.80632813577446</v>
+        <v>-18.74382695575201</v>
       </c>
       <c r="F48">
-        <v>-4.379002139073484</v>
+        <v>-5.015946486380414</v>
       </c>
       <c r="G48">
-        <v>2.116480270770825</v>
+        <v>-0.7263580158032072</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.825221330206443</v>
       </c>
       <c r="E49">
-        <v>-15.22282973141212</v>
+        <v>-18.36322230082934</v>
       </c>
       <c r="F49">
-        <v>-4.650180102974181</v>
+        <v>-5.679011687203644</v>
       </c>
       <c r="G49">
-        <v>2.472466543154195</v>
+        <v>0.04938225714097438</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.951085361700692</v>
       </c>
       <c r="E50">
-        <v>-14.26450953343491</v>
+        <v>-17.05711077058904</v>
       </c>
       <c r="F50">
-        <v>-4.620251228584206</v>
+        <v>-4.831834338886916</v>
       </c>
       <c r="G50">
-        <v>1.880739633464863</v>
+        <v>0.4057194473515072</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.030618315475619</v>
       </c>
       <c r="E51">
-        <v>-14.89374552527472</v>
+        <v>-18.40799079486917</v>
       </c>
       <c r="F51">
-        <v>-4.628039102423379</v>
+        <v>-5.41550044363959</v>
       </c>
       <c r="G51">
-        <v>2.078336165067342</v>
+        <v>1.067626611927849</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.063668751551006</v>
       </c>
       <c r="E52">
-        <v>-14.31191359934721</v>
+        <v>-17.40327638068338</v>
       </c>
       <c r="F52">
-        <v>-4.828754822734345</v>
+        <v>-5.404404999996021</v>
       </c>
       <c r="G52">
-        <v>2.227360372517635</v>
+        <v>-0.3610459366357103</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.050402108358705</v>
       </c>
       <c r="E53">
-        <v>-13.48787171264544</v>
+        <v>-17.15648360421336</v>
       </c>
       <c r="F53">
-        <v>-5.190112960724951</v>
+        <v>-5.425803242472481</v>
       </c>
       <c r="G53">
-        <v>1.843509238330219</v>
+        <v>0.4603302065673247</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.99116132016796</v>
       </c>
       <c r="E54">
-        <v>-13.72610114476695</v>
+        <v>-16.5246754391372</v>
       </c>
       <c r="F54">
-        <v>-5.175067754528277</v>
+        <v>-5.357874136494495</v>
       </c>
       <c r="G54">
-        <v>2.39835667071207</v>
+        <v>0.5275442126511476</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.885669924215307</v>
       </c>
       <c r="E55">
-        <v>-14.21441555396206</v>
+        <v>-15.73779421014237</v>
       </c>
       <c r="F55">
-        <v>-5.084869367820339</v>
+        <v>-5.697073853169231</v>
       </c>
       <c r="G55">
-        <v>2.83933126817961</v>
+        <v>0.4983054744483044</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.732506732937173</v>
       </c>
       <c r="E56">
-        <v>-12.98931842371899</v>
+        <v>-13.700152988703</v>
       </c>
       <c r="F56">
-        <v>-4.879351059320804</v>
+        <v>-5.592329919480939</v>
       </c>
       <c r="G56">
-        <v>3.160563433491711</v>
+        <v>0.910905386098751</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.529024026896937</v>
       </c>
       <c r="E57">
-        <v>-13.41057066133451</v>
+        <v>-14.98072845401405</v>
       </c>
       <c r="F57">
-        <v>-4.631165337900457</v>
+        <v>-5.707465339533386</v>
       </c>
       <c r="G57">
-        <v>2.19372522983864</v>
+        <v>1.203150414668994</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.273663451510268</v>
       </c>
       <c r="E58">
-        <v>-12.98190531176843</v>
+        <v>-14.61978643323268</v>
       </c>
       <c r="F58">
-        <v>-5.048321394556785</v>
+        <v>-5.68841335737065</v>
       </c>
       <c r="G58">
-        <v>2.801882377039374</v>
+        <v>-0.8449914152029903</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.9663369580959208</v>
       </c>
       <c r="E59">
-        <v>-12.38737101624941</v>
+        <v>-15.49313434492996</v>
       </c>
       <c r="F59">
-        <v>-5.038750267856827</v>
+        <v>-6.122217726536556</v>
       </c>
       <c r="G59">
-        <v>3.766429683179271</v>
+        <v>0.3590573079754797</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.6113764172435751</v>
       </c>
       <c r="E60">
-        <v>-12.5744015212402</v>
+        <v>-13.80280896598288</v>
       </c>
       <c r="F60">
-        <v>-4.902404274478898</v>
+        <v>-5.826729480907385</v>
       </c>
       <c r="G60">
-        <v>2.293409066571634</v>
+        <v>-0.2608522758896678</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.2183422478863019</v>
       </c>
       <c r="E61">
-        <v>-12.05428816756323</v>
+        <v>-14.60858298853771</v>
       </c>
       <c r="F61">
-        <v>-4.980001113217685</v>
+        <v>-6.195495007390981</v>
       </c>
       <c r="G61">
-        <v>2.767902937624295</v>
+        <v>-0.06897636697904909</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.2004334062166946</v>
       </c>
       <c r="E62">
-        <v>-11.43486990737205</v>
+        <v>-13.91007040132856</v>
       </c>
       <c r="F62">
-        <v>-5.00714820816719</v>
+        <v>-5.749591125031118</v>
       </c>
       <c r="G62">
-        <v>2.299639513276543</v>
+        <v>-0.2030898773204642</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.6305092555482675</v>
       </c>
       <c r="E63">
-        <v>-12.44278595268127</v>
+        <v>-12.34824047234913</v>
       </c>
       <c r="F63">
-        <v>-5.067770095051339</v>
+        <v>-6.050395475491941</v>
       </c>
       <c r="G63">
-        <v>2.809294688501803</v>
+        <v>-0.8895414265249626</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.057011620126332</v>
       </c>
       <c r="E64">
-        <v>-11.16186632334564</v>
+        <v>-13.28825204991332</v>
       </c>
       <c r="F64">
-        <v>-5.181887984053117</v>
+        <v>-5.999773107757877</v>
       </c>
       <c r="G64">
-        <v>2.212638376504496</v>
+        <v>-0.9481711880254553</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.463820443425728</v>
       </c>
       <c r="E65">
-        <v>-11.06205422774257</v>
+        <v>-13.33458739595981</v>
       </c>
       <c r="F65">
-        <v>-5.010956229040864</v>
+        <v>-5.83043297719064</v>
       </c>
       <c r="G65">
-        <v>2.106475802151147</v>
+        <v>-1.543158985070969</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.834398723503724</v>
       </c>
       <c r="E66">
-        <v>-11.73855843127444</v>
+        <v>-14.40786290662173</v>
       </c>
       <c r="F66">
-        <v>-4.907613083234779</v>
+        <v>-5.857006770598757</v>
       </c>
       <c r="G66">
-        <v>2.012512588110013</v>
+        <v>-1.242783256656277</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.153812475958885</v>
       </c>
       <c r="E67">
-        <v>-11.9434537662255</v>
+        <v>-13.26582251815333</v>
       </c>
       <c r="F67">
-        <v>-4.951781849363427</v>
+        <v>-6.201216540936985</v>
       </c>
       <c r="G67">
-        <v>0.5392701649512461</v>
+        <v>-1.828729953834041</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.410015283644289</v>
       </c>
       <c r="E68">
-        <v>-11.48504992785105</v>
+        <v>-14.37644435395651</v>
       </c>
       <c r="F68">
-        <v>-5.094292418017203</v>
+        <v>-5.614172391466679</v>
       </c>
       <c r="G68">
-        <v>1.572431837938077</v>
+        <v>-2.194518751559193</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.59445009150738</v>
       </c>
       <c r="E69">
-        <v>-11.96053969865643</v>
+        <v>-13.54401120491853</v>
       </c>
       <c r="F69">
-        <v>-4.889490736444404</v>
+        <v>-6.052789246983127</v>
       </c>
       <c r="G69">
-        <v>1.455897324410192</v>
+        <v>-1.451470115815315</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.702014596548823</v>
       </c>
       <c r="E70">
-        <v>-11.25368566232516</v>
+        <v>-13.32078913565843</v>
       </c>
       <c r="F70">
-        <v>-4.827002452138911</v>
+        <v>-5.912111817926472</v>
       </c>
       <c r="G70">
-        <v>0.5634901161165541</v>
+        <v>-1.616080371664496</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.731207244212896</v>
       </c>
       <c r="E71">
-        <v>-12.0431707638744</v>
+        <v>-12.87217585808857</v>
       </c>
       <c r="F71">
-        <v>-5.321402181114882</v>
+        <v>-5.71365604595684</v>
       </c>
       <c r="G71">
-        <v>0.8675604133530733</v>
+        <v>-2.967296086245727</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.684423108123898</v>
       </c>
       <c r="E72">
-        <v>-13.06146607160919</v>
+        <v>-14.44968336408256</v>
       </c>
       <c r="F72">
-        <v>-5.002618017396076</v>
+        <v>-5.841446068126606</v>
       </c>
       <c r="G72">
-        <v>0.7175629055142352</v>
+        <v>-1.941712251998288</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.567919876578475</v>
       </c>
       <c r="E73">
-        <v>-12.46728499706276</v>
+        <v>-13.17510359835767</v>
       </c>
       <c r="F73">
-        <v>-5.276657737885971</v>
+        <v>-6.071895866999947</v>
       </c>
       <c r="G73">
-        <v>0.3824727965747449</v>
+        <v>-3.707338746639948</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.390879658803146</v>
       </c>
       <c r="E74">
-        <v>-11.92559346473924</v>
+        <v>-14.37990410809837</v>
       </c>
       <c r="F74">
-        <v>-4.99628240188136</v>
+        <v>-5.956793704771723</v>
       </c>
       <c r="G74">
-        <v>0.332642465117635</v>
+        <v>-2.192423176232835</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.165591983592445</v>
       </c>
       <c r="E75">
-        <v>-12.56049910603665</v>
+        <v>-14.78377153399844</v>
       </c>
       <c r="F75">
-        <v>-4.992466462478109</v>
+        <v>-5.945497130476894</v>
       </c>
       <c r="G75">
-        <v>0.3809631878088372</v>
+        <v>-2.818271878795435</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.904703522506346</v>
       </c>
       <c r="E76">
-        <v>-13.51861099420951</v>
+        <v>-16.01341525214522</v>
       </c>
       <c r="F76">
-        <v>-4.79465525881606</v>
+        <v>-6.060858228622291</v>
       </c>
       <c r="G76">
-        <v>0.04288034570184577</v>
+        <v>-1.99153596236432</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.622036564570761</v>
       </c>
       <c r="E77">
-        <v>-13.45763056322222</v>
+        <v>-15.02482673390074</v>
       </c>
       <c r="F77">
-        <v>-4.998272328364109</v>
+        <v>-5.666601767650261</v>
       </c>
       <c r="G77">
-        <v>-0.1028399373002541</v>
+        <v>-3.539755620896501</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.33052482687757</v>
       </c>
       <c r="E78">
-        <v>-13.79323124345666</v>
+        <v>-14.41048489307217</v>
       </c>
       <c r="F78">
-        <v>-5.02432745808492</v>
+        <v>-6.458169658305205</v>
       </c>
       <c r="G78">
-        <v>0.527878577750614</v>
+        <v>-2.618781715144492</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.04035195064759</v>
       </c>
       <c r="E79">
-        <v>-13.92222935403916</v>
+        <v>-17.54700108873882</v>
       </c>
       <c r="F79">
-        <v>-5.404925247389243</v>
+        <v>-6.176564574657255</v>
       </c>
       <c r="G79">
-        <v>0.2971534169366478</v>
+        <v>-3.045891747893565</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.761852891831727</v>
       </c>
       <c r="E80">
-        <v>-14.94460481685486</v>
+        <v>-16.05885396033819</v>
       </c>
       <c r="F80">
-        <v>-5.504120667402793</v>
+        <v>-6.11613906730662</v>
       </c>
       <c r="G80">
-        <v>-0.7641644458616842</v>
+        <v>-3.032493970096134</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.5022930360065799</v>
       </c>
       <c r="E81">
-        <v>-15.62349552618877</v>
+        <v>-17.47453191919407</v>
       </c>
       <c r="F81">
-        <v>-5.532918775769144</v>
+        <v>-6.529420587440826</v>
       </c>
       <c r="G81">
-        <v>-0.1092657061919794</v>
+        <v>-2.557635939034153</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.2700255454946098</v>
       </c>
       <c r="E82">
-        <v>-16.63074135734485</v>
+        <v>-17.7194408504769</v>
       </c>
       <c r="F82">
-        <v>-5.497063673843594</v>
+        <v>-6.444140795379764</v>
       </c>
       <c r="G82">
-        <v>0.611562547892311</v>
+        <v>-3.49665231797519</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.0718772199744879</v>
       </c>
       <c r="E83">
-        <v>-16.68256974236264</v>
+        <v>-18.53739646811236</v>
       </c>
       <c r="F83">
-        <v>-5.544296119065661</v>
+        <v>-6.726169520360093</v>
       </c>
       <c r="G83">
-        <v>-0.7090107571774262</v>
+        <v>-2.998997870329788</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.08814305780728027</v>
       </c>
       <c r="E84">
-        <v>-18.04567211798947</v>
+        <v>-19.15359498328408</v>
       </c>
       <c r="F84">
-        <v>-5.482385887419301</v>
+        <v>-6.436737762078041</v>
       </c>
       <c r="G84">
-        <v>0.09229023787546824</v>
+        <v>-3.078354957451658</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2042627808757046</v>
       </c>
       <c r="E85">
-        <v>-18.45079393118967</v>
+        <v>-19.85912670520511</v>
       </c>
       <c r="F85">
-        <v>-5.629134453102794</v>
+        <v>-6.563476203519957</v>
       </c>
       <c r="G85">
-        <v>-0.2683241771718029</v>
+        <v>-2.432159642004697</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.2748353421064821</v>
       </c>
       <c r="E86">
-        <v>-19.88239853313053</v>
+        <v>-22.19526229086007</v>
       </c>
       <c r="F86">
-        <v>-5.676364522765986</v>
+        <v>-6.566244917386624</v>
       </c>
       <c r="G86">
-        <v>0.3486158473446184</v>
+        <v>-3.128668628557501</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.2971457929346352</v>
       </c>
       <c r="E87">
-        <v>-20.9715871014554</v>
+        <v>-22.78800331067206</v>
       </c>
       <c r="F87">
-        <v>-5.677017009603148</v>
+        <v>-6.814637312428935</v>
       </c>
       <c r="G87">
-        <v>-0.6888329821155683</v>
+        <v>-2.954878229927921</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.2700034753487464</v>
       </c>
       <c r="E88">
-        <v>-22.78425826266772</v>
+        <v>-24.97444565952947</v>
       </c>
       <c r="F88">
-        <v>-5.674243940545214</v>
+        <v>-6.45184433687894</v>
       </c>
       <c r="G88">
-        <v>-0.2303919463828336</v>
+        <v>-3.330621838089662</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.1955902815099442</v>
       </c>
       <c r="E89">
-        <v>-24.81290140625385</v>
+        <v>-26.32613175218296</v>
       </c>
       <c r="F89">
-        <v>-5.791753335764905</v>
+        <v>-6.62569407004039</v>
       </c>
       <c r="G89">
-        <v>-0.04347854523558242</v>
+        <v>-2.6992379033854</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.07438276562742333</v>
       </c>
       <c r="E90">
-        <v>-26.21453656721194</v>
+        <v>-26.31851938737607</v>
       </c>
       <c r="F90">
-        <v>-5.984833218004578</v>
+        <v>-6.658576555962659</v>
       </c>
       <c r="G90">
-        <v>-0.02170177667825654</v>
+        <v>-3.048162782133505</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.0881194607999132</v>
       </c>
       <c r="E91">
-        <v>-27.70796389630552</v>
+        <v>-29.2756627275989</v>
       </c>
       <c r="F91">
-        <v>-5.646390512757423</v>
+        <v>-6.428103001500587</v>
       </c>
       <c r="G91">
-        <v>-0.8236383964746911</v>
+        <v>-3.23814505899566</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.2868692152787689</v>
       </c>
       <c r="E92">
-        <v>-29.42592428788441</v>
+        <v>-30.52102930750031</v>
       </c>
       <c r="F92">
-        <v>-5.709281058365438</v>
+        <v>-6.625326650268008</v>
       </c>
       <c r="G92">
-        <v>-1.379445887062931</v>
+        <v>-3.595253606316843</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5160005260910143</v>
       </c>
       <c r="E93">
-        <v>-31.32237901094964</v>
+        <v>-33.50765301351307</v>
       </c>
       <c r="F93">
-        <v>-5.807143789851145</v>
+        <v>-6.584392207545165</v>
       </c>
       <c r="G93">
-        <v>-1.765799793678035</v>
+        <v>-3.572665754102396</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.7674995661515933</v>
       </c>
       <c r="E94">
-        <v>-33.30307240750555</v>
+        <v>-34.44338291890301</v>
       </c>
       <c r="F94">
-        <v>-5.717883748898105</v>
+        <v>-5.967968333711064</v>
       </c>
       <c r="G94">
-        <v>-2.027025010545307</v>
+        <v>-3.189317822836949</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.036250097167568</v>
       </c>
       <c r="E95">
-        <v>-35.47186955739207</v>
+        <v>-37.34670534554468</v>
       </c>
       <c r="F95">
-        <v>-5.592093947299539</v>
+        <v>-6.305493677306702</v>
       </c>
       <c r="G95">
-        <v>-2.298049442208821</v>
+        <v>-4.187576414203244</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.32121713842088</v>
       </c>
       <c r="E96">
-        <v>-38.06469037098681</v>
+        <v>-38.59311800294186</v>
       </c>
       <c r="F96">
-        <v>-5.184809129614145</v>
+        <v>-6.105376993758252</v>
       </c>
       <c r="G96">
-        <v>-2.898701582672028</v>
+        <v>-4.45318479336451</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.615714249408848</v>
       </c>
       <c r="E97">
-        <v>-39.95020430084951</v>
+        <v>-41.36887784526146</v>
       </c>
       <c r="F97">
-        <v>-5.499182672358453</v>
+        <v>-6.024919982136182</v>
       </c>
       <c r="G97">
-        <v>-2.283761127661327</v>
+        <v>-5.387195627450169</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.935042817723033</v>
       </c>
       <c r="E98">
-        <v>-42.95761370255747</v>
+        <v>-43.79228391775524</v>
       </c>
       <c r="F98">
-        <v>-5.219042516682284</v>
+        <v>-6.590798297973118</v>
       </c>
       <c r="G98">
-        <v>-2.70995744984156</v>
+        <v>-5.931704226112876</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.264850951727761</v>
       </c>
       <c r="E99">
-        <v>-44.8296305156403</v>
+        <v>-45.64719215603709</v>
       </c>
       <c r="F99">
-        <v>-5.40375251315886</v>
+        <v>-5.827944975197485</v>
       </c>
       <c r="G99">
-        <v>-3.36042336903418</v>
+        <v>-6.559410144723008</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.644366220432118</v>
       </c>
       <c r="E100">
-        <v>-47.61699230836756</v>
+        <v>-47.45899385023993</v>
       </c>
       <c r="F100">
-        <v>-5.320344265563368</v>
+        <v>-5.539736629735111</v>
       </c>
       <c r="G100">
-        <v>-4.482224898834997</v>
+        <v>-5.882830642316615</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.033723951658682</v>
       </c>
       <c r="E101">
-        <v>-49.59052731963584</v>
+        <v>-50.1351317928648</v>
       </c>
       <c r="F101">
-        <v>-5.419953032820848</v>
+        <v>-5.604980562333469</v>
       </c>
       <c r="G101">
-        <v>-4.682721468329878</v>
+        <v>-7.265225074786703</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.5189853772593</v>
       </c>
       <c r="E102">
-        <v>-51.90619080642062</v>
+        <v>-52.93466612372467</v>
       </c>
       <c r="F102">
-        <v>-5.094113459248758</v>
+        <v>-5.003392449588725</v>
       </c>
       <c r="G102">
-        <v>-5.227749822642251</v>
+        <v>-6.777402947392936</v>
       </c>
     </row>
   </sheetData>
